--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.147.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.147.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.147" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.147" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.147.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.147.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0147.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0147.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -847,7 +847,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.147.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.147.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.147" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.147" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -595,18 +595,18 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The following is the form:â€”</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L22: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: motion :â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]140</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]140</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 140</t>
@@ -614,7 +614,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L125: isolated marker/symbol line :: 7</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]140</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -658,16 +658,8 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L37: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: served with a writ of subpo Ã¦ na therein; therefore we com-</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The following is the form :â€”</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -675,7 +667,11 @@
           <t>L63: isolated marker/symbol line :: 140</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>L125: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr">
         <is>
@@ -713,16 +709,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”â€”, in the County of</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The following memorandum to be placed at foot :â€”-</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr"/>
@@ -750,12 +738,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -764,16 +752,8 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”) ; and, if you neglect</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: to whom the cause stands referred] in the City of â€”â€”</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr"/>
@@ -815,16 +795,8 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: The persons served with such last mentioned subpo Ã¦ na</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€”, in the County of - ---------------------------); and, if you neglect</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr"/>
@@ -832,7 +804,7 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€”, in the County of - ---------------------------); and, if you neglect</t>
+          <t>L110: punctuation artifact: double/multiple hyphen :: —, in the County of - ---------------------------); and, if you neglect</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -866,16 +838,8 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The following is the form:â€”</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Masterâ€™s office, having appeared are to be at liberty to attend, and to be</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr"/>
@@ -913,11 +877,7 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L121: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: served with a writ of subpo Ã¦ na therein; therefore we com-</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
@@ -956,11 +916,7 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”â€”, in the County of</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
@@ -985,12 +941,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -999,11 +955,7 @@
       <c r="G10" s="1" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L153: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”) ; and, if you neglect</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
@@ -1033,7 +985,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1042,11 +994,7 @@
       <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L160: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: The persons served with such last mentioned subpo Ã¦ na</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
@@ -1076,7 +1024,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
